--- a/data_extactor/batch/51_100.xlsx
+++ b/data_extactor/batch/51_100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB245942-EAAB-4B8C-89C7-FDBAF227BE65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF73D6D-632D-4424-8A4D-BE1E7B906524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="544">
   <si>
     <t>11-9179.00</t>
   </si>
@@ -1576,6 +1576,87 @@
   </si>
   <si>
     <t>Analyze financial information obtained from clients to determine strategies for meeting clients' financial objectives. | Answer clients' questions about the purposes and details of financial plans and strategies. | Conduct seminars or workshops on financial planning topics, such as retirement planning, estate planning, or the evaluation of severance packages. | Contact clients periodically to determine any changes in their financial status. | Devise debt liquidation plans that include payoff priorities and timelines. | Explain to clients the personal financial advisor's responsibilities and the types of services to be provided. | Guide clients in the gathering of information, such as bank account records, income tax returns, life and disability insurance records, pension plans, or wills. | Implement financial planning recommendations, or refer clients to someone who can assist them with plan implementation. | Inform clients about tax benefits, government rebates, or other financial benefits of alternative-fuel vehicle purchases or energy-efficient home construction, improvements, or remodeling. | Interview clients to determine their current income, expenses, insurance coverage, tax status, financial objectives, risk tolerance, or other information needed to develop a financial plan. | Investigate available investment opportunities to determine compatibility with client financial plans. | Manage client portfolios, keeping client plans up-to-date. | Meet with clients' other advisors, such as attorneys, accountants, trust officers, or investment bankers, to fully understand clients' financial goals and circumstances. | Monitor financial market trends to ensure that client plans are responsive. | Open accounts for clients, and disburse funds from accounts to creditors as agent for clients. | Prepare or interpret for clients information, such as investment performance reports, financial document summaries, or income projections. | Recommend environmentally responsible investments, such as cleantech, alternative energy, or conservation technologies, companies, or funds. | Recommend financial products, such as stocks, bonds, mutual funds, or insurance. | Recommend to clients strategies in cash management, insurance coverage, investment planning, or other areas to help them achieve their financial goals. | Recruit and maintain client bases. | Review clients' accounts and plans regularly to determine whether life changes, economic changes, environmental concerns, or financial performance indicate a need for plan reassessment.</t>
+  </si>
+  <si>
+    <t>Barber Shop Manager | Beauty Salon Manager | Day Spa Manager | Grooming Salon Manager | Personal Care Services Manager | Personal Services Director | Pet Services Manager | Salon Director | Wellness Center Manager | Personal Service Operations Manager</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | Microsoft Office software | Email software | Microsoft Access | Microsoft SharePoint | Web browser software | Database software | Google Docs | Calendar management software | Spreadsheet programs | Adobe Acrobat | Microsoft Project | SAP software | Enterprise resource planning ERP system | Human resources management system HRMS | Microsoft Power BI | Scheduling software | Inventory management systems</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Monitoring | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administration and Management | Personnel and Human Resources | Sales and Marketing | English Language | Economics and Accounting | Education and Training | Psychology | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Written Expression</t>
+  </si>
+  <si>
+    <t>Contact With Others | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Spend Time Standing | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Telephone Conversations | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Public Speaking | Conflict Situations | Level of Competition | E-Mail | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Fitness and Wellness Coordinators | Spa Managers | Funeral Home Managers | Lodging Managers | Food Service Managers | Gambling Managers | Entertainment and Recreation Managers, Except Gambling | General and Operations Managers | Administrative Services Managers | Property, Real Estate, and Community Association Managers | Social and Community Service Managers | Human Resources Managers | Sales Managers | Marketing Managers | Chief Executives | Medical and Health Services Managers | Purchasing Managers | Training and Development Managers | First-Line Supervisors of Personal Service Workers | Personal Care and Service Workers, All Other</t>
+  </si>
+  <si>
+    <t>Plan, direct, and coordinate the operations of personal service establishments not classified separately. | Recruit, hire, train, schedule, and evaluate service staff. | Establish service standards, pricing, and operating procedures. | Monitor revenue, expenses, and profitability and prepare operating budgets. | Resolve customer complaints and ensure client satisfaction with services provided. | Order and maintain inventories of supplies, products, and equipment. | Ensure compliance with health, safety, sanitation, and licensing requirements. | Develop and implement marketing, promotion, and client retention programs. | Inspect facilities and equipment to verify cleanliness, safety, and working order. | Maintain records of appointments, sales, payroll, and inventory. | Negotiate contracts with suppliers, vendors, and service providers. | Analyze service trends and client feedback to adjust offerings. | Train staff on new products, techniques, and customer service practices.</t>
+  </si>
+  <si>
+    <t>Business Manager | Department Manager | Director of Operations | District Manager | Division Manager | General Manager | Operations Director | Program Manager | Regional Manager | Unit Manager</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | Microsoft Office software | Email software | Microsoft Access | Microsoft SharePoint | Web browser software | Database software | Google Docs | Calendar management software | Spreadsheet programs | Adobe Acrobat | Microsoft Project | SAP software | Enterprise resource planning ERP system | Human resources management system HRMS | Microsoft Power BI</t>
+  </si>
+  <si>
+    <t>Administration and Management | Personnel and Human Resources | English Language | Customer and Personal Service | Economics and Accounting | Education and Training | Computers and Electronics | Law and Government | Sales and Marketing | Communications and Media</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Public Speaking | Conflict Situations | Level of Competition</t>
+  </si>
+  <si>
+    <t>Chief Executives | General and Operations Managers | Administrative Services Managers | Facilities Managers | Financial Managers | Industrial Production Managers | Purchasing Managers | Transportation, Storage, and Distribution Managers | Human Resources Managers | Training and Development Managers | Compensation and Benefits Managers | Marketing Managers | Sales Managers | Public Relations Managers | Fundraising Managers | Computer and Information Systems Managers | Medical and Health Services Managers | Social and Community Service Managers | Property, Real Estate, and Community Association Managers | Construction Managers</t>
+  </si>
+  <si>
+    <t>Plan, direct, and coordinate the operations of organizations or departments not classified separately. | Establish departmental goals, objectives, policies, and operating procedures. | Direct and coordinate the activities of supervisory and professional staff. | Prepare, justify, and administer operating and capital budgets. | Analyze operating and financial data to evaluate performance against objectives. | Recruit, hire, train, and evaluate personnel and recommend personnel actions. | Negotiate and approve contracts, agreements, and purchases of goods and services. | Ensure compliance with applicable laws, regulations, and organizational policies. | Prepare reports and presentations for senior management and governing bodies. | Identify process improvements and implement changes to increase efficiency. | Resolve escalated operational problems, customer issues, and staff disputes. | Represent the organization in dealings with clients, vendors, and outside agencies. | Monitor industry trends and competitor activity to inform planning decisions. | Direct the allocation of staff, equipment, and facilities across projects.</t>
+  </si>
+  <si>
+    <t>Program Coordinator | Project Administrator | Project Analyst | Project Controls Specialist | Project Coordinator | Project Lead | Project Management Specialist | Project Manager | Project Planner | Project Scheduler</t>
+  </si>
+  <si>
+    <t>Administration and Management | English Language | Customer and Personal Service | Computers and Electronics | Economics and Accounting | Mathematics | Personnel and Human Resources | Engineering and Technology | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization | Mathematical Reasoning | Number Facility | Perceptual Speed | Flexibility of Closure</t>
+  </si>
+  <si>
+    <t>Administrative Analyst | Business Analyst | Business Consultant | Business Development Specialist | Business Operations Analyst | Business Process Analyst | Contract Specialist | Operations Coordinator | Operations Specialist | Program Analyst</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | Microsoft Office software | Email software | Microsoft Access | Microsoft SharePoint | Web browser software | Database software | Google Docs | Calendar management software | Spreadsheet programs | Adobe Acrobat | Microsoft Project | Microsoft Power BI | Tableau | Structured query language SQL | Enterprise resource planning ERP system</t>
+  </si>
+  <si>
+    <t>Administration and Management | English Language | Customer and Personal Service | Economics and Accounting | Computers and Electronics | Mathematics | Personnel and Human Resources | Law and Government | Sales and Marketing | Communications and Media</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Level of Competition</t>
+  </si>
+  <si>
+    <t>Management Analysts | Project Management Specialists | Business Continuity Planners | Sustainability Specialists | Security Management Specialists | Online Merchants | Logisticians | Logistics Analysts | Compliance Officers | Cost Estimators | Human Resources Specialists | Training and Development Specialists | Meeting, Convention, and Event Planners | Market Research Analysts and Marketing Specialists | Fundraisers | Labor Relations Specialists | Compensation, Benefits, and Job Analysis Specialists | Purchasing Agents, Except Wholesale, Retail, and Farm Products | General and Operations Managers | Accountants and Auditors</t>
+  </si>
+  <si>
+    <t>Perform business operations and analysis duties not classified separately. | Analyze business processes and recommend improvements to efficiency and effectiveness. | Collect, compile, and interpret operational and financial data to support decisions. | Prepare reports, dashboards, and presentations summarizing findings and recommendations. | Develop and maintain operating procedures, standards, and documentation. | Coordinate projects across departments and track progress against milestones. | Draft, review, and administer contracts, proposals, and service agreements. | Monitor compliance with internal policies and external regulatory requirements. | Confer with managers and staff to identify operational requirements and constraints. | Evaluate vendor proposals and support procurement and sourcing decisions. | Forecast resource, staffing, and budget requirements for business units. | Design and administer surveys, audits, and quality reviews of business activities. | Maintain databases and records supporting business operations reporting. | Train staff on new processes, systems, and reporting tools.</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Mathematics | Active Learning | Writing | Speaking | Active Listening | Science | Monitoring</t>
+  </si>
+  <si>
+    <t>Economics and Accounting | Mathematics | English Language | Administration and Management | Computers and Electronics | Law and Government | Customer and Personal Service | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Level of Competition | Coordinate or Lead Others in Accomplishing Work Activities</t>
   </si>
 </sst>
 </file>
@@ -1903,8 +1984,32 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D1" t="s">
+        <v>518</v>
+      </c>
+      <c r="E1" t="s">
+        <v>519</v>
+      </c>
+      <c r="F1" t="s">
+        <v>520</v>
+      </c>
+      <c r="G1" t="s">
+        <v>521</v>
+      </c>
+      <c r="H1" t="s">
+        <v>522</v>
+      </c>
+      <c r="I1" t="s">
+        <v>523</v>
+      </c>
       <c r="J1" t="s">
         <v>2</v>
+      </c>
+      <c r="K1" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -1984,8 +2089,32 @@
       <c r="B4" t="s">
         <v>26</v>
       </c>
+      <c r="C4" t="s">
+        <v>525</v>
+      </c>
+      <c r="D4" t="s">
+        <v>526</v>
+      </c>
+      <c r="E4" t="s">
+        <v>519</v>
+      </c>
+      <c r="F4" t="s">
+        <v>527</v>
+      </c>
+      <c r="G4" t="s">
+        <v>528</v>
+      </c>
+      <c r="H4" t="s">
+        <v>529</v>
+      </c>
+      <c r="I4" t="s">
+        <v>530</v>
+      </c>
       <c r="J4" t="s">
         <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -2905,8 +3034,23 @@
       <c r="B31" t="s">
         <v>315</v>
       </c>
+      <c r="C31" t="s">
+        <v>532</v>
+      </c>
       <c r="D31" t="s">
         <v>316</v>
+      </c>
+      <c r="E31" t="s">
+        <v>519</v>
+      </c>
+      <c r="F31" t="s">
+        <v>533</v>
+      </c>
+      <c r="G31" t="s">
+        <v>534</v>
+      </c>
+      <c r="H31" t="s">
+        <v>529</v>
       </c>
       <c r="I31" t="s">
         <v>317</v>
@@ -3170,8 +3314,32 @@
       <c r="B39" t="s">
         <v>398</v>
       </c>
+      <c r="C39" t="s">
+        <v>535</v>
+      </c>
+      <c r="D39" t="s">
+        <v>536</v>
+      </c>
+      <c r="E39" t="s">
+        <v>519</v>
+      </c>
+      <c r="F39" t="s">
+        <v>537</v>
+      </c>
+      <c r="G39" t="s">
+        <v>534</v>
+      </c>
+      <c r="H39" t="s">
+        <v>538</v>
+      </c>
+      <c r="I39" t="s">
+        <v>539</v>
+      </c>
       <c r="J39" t="s">
         <v>399</v>
+      </c>
+      <c r="K39" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
@@ -3501,6 +3669,18 @@
       </c>
       <c r="D49" t="s">
         <v>502</v>
+      </c>
+      <c r="E49" t="s">
+        <v>541</v>
+      </c>
+      <c r="F49" t="s">
+        <v>542</v>
+      </c>
+      <c r="G49" t="s">
+        <v>534</v>
+      </c>
+      <c r="H49" t="s">
+        <v>543</v>
       </c>
       <c r="I49" t="s">
         <v>503</v>
